--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
@@ -1480,6 +1480,2344 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114872284</v>
+      </c>
+      <c r="B9" t="n">
+        <v>94034</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575548</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6338810</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114859545</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90240</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575515</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6338833</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114857989</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91446</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ekskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Aleurocystidiellum disciforme</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(DC.) Boidin &amp; al.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>575486</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6338913</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114872693</v>
+      </c>
+      <c r="B12" t="n">
+        <v>95090</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>575577</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6338984</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114872484</v>
+      </c>
+      <c r="B13" t="n">
+        <v>94034</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>575509</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6338990</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114872551</v>
+      </c>
+      <c r="B14" t="n">
+        <v>95129</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>575467</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6339004</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114872304</v>
+      </c>
+      <c r="B15" t="n">
+        <v>94209</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>575597</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6338786</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114872598</v>
+      </c>
+      <c r="B16" t="n">
+        <v>94209</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>575402</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6339055</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114872399</v>
+      </c>
+      <c r="B17" t="n">
+        <v>95129</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>575482</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6338794</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114872677</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95090</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>53</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>575558</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6338996</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114872706</v>
+      </c>
+      <c r="B19" t="n">
+        <v>95129</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>575651</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6338972</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114859291</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57382</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>575523</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6338795</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114872517</v>
+      </c>
+      <c r="B21" t="n">
+        <v>95090</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>53</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>575471</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6339012</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114857737</v>
+      </c>
+      <c r="B22" t="n">
+        <v>94316</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>575393</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6338961</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114872293</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90240</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>575560</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6338813</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114872557</v>
+      </c>
+      <c r="B24" t="n">
+        <v>94209</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>575467</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6339004</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114872751</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93956</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>575659</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6338884</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114872859</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>575587</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6338870</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114872595</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8404</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>575402</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6339055</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114872397</v>
+      </c>
+      <c r="B28" t="n">
+        <v>95090</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>575482</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6338794</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>114859353</v>
+      </c>
+      <c r="B29" t="n">
+        <v>95090</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>53</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>575517</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6338810</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114872575</v>
+      </c>
+      <c r="B30" t="n">
+        <v>94209</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>575452</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6338990</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115149792</v>
+        <v>115155013</v>
       </c>
       <c r="B33" t="n">
-        <v>90332</v>
+        <v>56478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,38 +4036,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hultemossen, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575468</v>
+        <v>575402</v>
       </c>
       <c r="R33" t="n">
-        <v>6338989</v>
+        <v>6339054</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4094,12 +4094,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4126,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115155013</v>
+        <v>115173026</v>
       </c>
       <c r="B34" t="n">
-        <v>56478</v>
+        <v>57281</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4138,38 +4143,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575402</v>
+        <v>575465</v>
       </c>
       <c r="R34" t="n">
-        <v>6339054</v>
+        <v>6338869</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4199,14 +4216,19 @@
           <t>2024-03-13</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-03-13</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4221,22 +4243,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115173026</v>
+        <v>115173318</v>
       </c>
       <c r="B35" t="n">
-        <v>57281</v>
+        <v>57414</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4249,33 +4271,33 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4285,10 +4307,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575465</v>
+        <v>575598</v>
       </c>
       <c r="R35" t="n">
-        <v>6338869</v>
+        <v>6338927</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4357,10 +4379,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115173318</v>
+        <v>115173297</v>
       </c>
       <c r="B36" t="n">
-        <v>57414</v>
+        <v>95242</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4369,39 +4391,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>2590</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4409,10 +4423,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575598</v>
+        <v>575651</v>
       </c>
       <c r="R36" t="n">
-        <v>6338927</v>
+        <v>6338902</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4463,6 +4477,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4481,10 +4496,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115173297</v>
+        <v>115173056</v>
       </c>
       <c r="B37" t="n">
-        <v>95242</v>
+        <v>90332</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4493,31 +4508,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4525,10 +4539,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575651</v>
+        <v>575620</v>
       </c>
       <c r="R37" t="n">
-        <v>6338902</v>
+        <v>6338869</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4598,10 +4612,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115173056</v>
+        <v>115173452</v>
       </c>
       <c r="B38" t="n">
-        <v>90332</v>
+        <v>99909</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4610,30 +4624,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4641,10 +4656,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575620</v>
+        <v>575502</v>
       </c>
       <c r="R38" t="n">
-        <v>6338869</v>
+        <v>6338880</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4714,10 +4729,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115173452</v>
+        <v>115173432</v>
       </c>
       <c r="B39" t="n">
-        <v>99909</v>
+        <v>94147</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4730,21 +4745,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4758,10 +4773,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575502</v>
+        <v>575531</v>
       </c>
       <c r="R39" t="n">
-        <v>6338880</v>
+        <v>6338883</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4831,10 +4846,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115173432</v>
+        <v>115173274</v>
       </c>
       <c r="B40" t="n">
-        <v>94147</v>
+        <v>96610</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4847,21 +4862,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2671</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4875,10 +4890,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575531</v>
+        <v>575592</v>
       </c>
       <c r="R40" t="n">
-        <v>6338883</v>
+        <v>6338890</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4948,10 +4963,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115173274</v>
+        <v>115173445</v>
       </c>
       <c r="B41" t="n">
-        <v>96610</v>
+        <v>95203</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4960,25 +4975,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4992,10 +5007,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575592</v>
+        <v>575507</v>
       </c>
       <c r="R41" t="n">
-        <v>6338890</v>
+        <v>6338888</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5065,7 +5080,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115173445</v>
+        <v>115173017</v>
       </c>
       <c r="B42" t="n">
         <v>95203</v>
@@ -5109,10 +5124,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575507</v>
+        <v>575465</v>
       </c>
       <c r="R42" t="n">
-        <v>6338888</v>
+        <v>6338869</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5182,10 +5197,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115173017</v>
+        <v>115474193</v>
       </c>
       <c r="B43" t="n">
-        <v>95203</v>
+        <v>95242</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5194,25 +5209,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5241,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575465</v>
+        <v>575542</v>
       </c>
       <c r="R43" t="n">
-        <v>6338869</v>
+        <v>6338926</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5256,22 +5271,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5299,10 +5314,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115474193</v>
+        <v>115473893</v>
       </c>
       <c r="B44" t="n">
-        <v>95242</v>
+        <v>99909</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5315,26 +5330,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2590</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -5343,10 +5362,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575542</v>
+        <v>575490</v>
       </c>
       <c r="R44" t="n">
-        <v>6338926</v>
+        <v>6338951</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5416,10 +5435,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115473893</v>
+        <v>115473966</v>
       </c>
       <c r="B45" t="n">
-        <v>99909</v>
+        <v>57414</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5428,35 +5447,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5464,10 +5487,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575490</v>
+        <v>575648</v>
       </c>
       <c r="R45" t="n">
-        <v>6338951</v>
+        <v>6338867</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5518,7 +5541,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5537,10 +5559,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115473966</v>
+        <v>115473932</v>
       </c>
       <c r="B46" t="n">
-        <v>57414</v>
+        <v>96610</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5549,39 +5571,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5643,6 +5657,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5658,123 +5673,6 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>115473932</v>
-      </c>
-      <c r="B47" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>575648</v>
-      </c>
-      <c r="R47" t="n">
-        <v>6338867</v>
-      </c>
-      <c r="S47" t="n">
-        <v>25</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Jan Brenander</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Jan Brenander</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5674,6 +5674,628 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123972269</v>
+      </c>
+      <c r="B47" t="n">
+        <v>95175</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>575366</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6338963</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123973813</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91391</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gökklint, Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>575666</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6338964</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123972648</v>
+      </c>
+      <c r="B49" t="n">
+        <v>90950</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>575416</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6338968</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123972575</v>
+      </c>
+      <c r="B50" t="n">
+        <v>95175</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>575396</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6338959</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123972955</v>
+      </c>
+      <c r="B51" t="n">
+        <v>100682</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>575485</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6338876</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123973504</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>575611</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6338932</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -5679,7 +5679,7 @@
         <v>123972269</v>
       </c>
       <c r="B47" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5987,10 +5987,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123972575</v>
+        <v>123972955</v>
       </c>
       <c r="B50" t="n">
-        <v>95175</v>
+        <v>100257</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6003,21 +6003,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6027,10 +6027,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575396</v>
+        <v>575485</v>
       </c>
       <c r="R50" t="n">
-        <v>6338959</v>
+        <v>6338876</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6089,10 +6089,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123972955</v>
+        <v>123973504</v>
       </c>
       <c r="B51" t="n">
-        <v>100682</v>
+        <v>57507</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6101,41 +6101,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575485</v>
+        <v>575611</v>
       </c>
       <c r="R51" t="n">
-        <v>6338876</v>
+        <v>6338932</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6191,10 +6196,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123973504</v>
+        <v>123972575</v>
       </c>
       <c r="B52" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6203,46 +6208,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575611</v>
+        <v>575396</v>
       </c>
       <c r="R52" t="n">
-        <v>6338932</v>
+        <v>6338959</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -5676,10 +5676,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123972269</v>
+        <v>123972955</v>
       </c>
       <c r="B47" t="n">
-        <v>95683</v>
+        <v>100257</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5692,21 +5692,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575366</v>
+        <v>575485</v>
       </c>
       <c r="R47" t="n">
-        <v>6338963</v>
+        <v>6338876</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5752,11 +5752,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5783,10 +5778,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123973813</v>
+        <v>123972575</v>
       </c>
       <c r="B48" t="n">
-        <v>91391</v>
+        <v>95683</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5799,34 +5794,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4217</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575666</v>
+        <v>575396</v>
       </c>
       <c r="R48" t="n">
-        <v>6338964</v>
+        <v>6338959</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5885,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123972648</v>
+        <v>123972269</v>
       </c>
       <c r="B49" t="n">
-        <v>90950</v>
+        <v>95683</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5897,25 +5892,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5445</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5925,10 +5920,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575416</v>
+        <v>575366</v>
       </c>
       <c r="R49" t="n">
-        <v>6338968</v>
+        <v>6338963</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5961,6 +5956,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5987,10 +5987,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123972955</v>
+        <v>123973813</v>
       </c>
       <c r="B50" t="n">
-        <v>100257</v>
+        <v>91391</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6003,34 +6003,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>4217</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575485</v>
+        <v>575666</v>
       </c>
       <c r="R50" t="n">
-        <v>6338876</v>
+        <v>6338964</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6089,10 +6089,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123973504</v>
+        <v>123972648</v>
       </c>
       <c r="B51" t="n">
-        <v>57507</v>
+        <v>90950</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6105,42 +6105,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575611</v>
+        <v>575416</v>
       </c>
       <c r="R51" t="n">
-        <v>6338932</v>
+        <v>6338968</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6196,10 +6191,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123972575</v>
+        <v>123973504</v>
       </c>
       <c r="B52" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6208,41 +6203,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575396</v>
+        <v>575611</v>
       </c>
       <c r="R52" t="n">
-        <v>6338959</v>
+        <v>6338932</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -5676,10 +5676,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123972955</v>
+        <v>123973504</v>
       </c>
       <c r="B47" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5688,41 +5688,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575485</v>
+        <v>575611</v>
       </c>
       <c r="R47" t="n">
-        <v>6338876</v>
+        <v>6338932</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5778,10 +5783,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123972575</v>
+        <v>123973813</v>
       </c>
       <c r="B48" t="n">
-        <v>95683</v>
+        <v>91391</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5794,34 +5799,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>4217</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575396</v>
+        <v>575666</v>
       </c>
       <c r="R48" t="n">
-        <v>6338959</v>
+        <v>6338964</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5880,10 +5885,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123972269</v>
+        <v>123972648</v>
       </c>
       <c r="B49" t="n">
-        <v>95683</v>
+        <v>90950</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5892,25 +5897,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>5445</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5920,10 +5925,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575366</v>
+        <v>575416</v>
       </c>
       <c r="R49" t="n">
-        <v>6338963</v>
+        <v>6338968</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5956,11 +5961,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5987,10 +5987,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123973813</v>
+        <v>123972955</v>
       </c>
       <c r="B50" t="n">
-        <v>91391</v>
+        <v>100257</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6003,34 +6003,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4217</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575666</v>
+        <v>575485</v>
       </c>
       <c r="R50" t="n">
-        <v>6338964</v>
+        <v>6338876</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6089,10 +6089,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123972648</v>
+        <v>123972269</v>
       </c>
       <c r="B51" t="n">
-        <v>90950</v>
+        <v>95683</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6101,25 +6101,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5445</v>
+        <v>2180</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575416</v>
+        <v>575366</v>
       </c>
       <c r="R51" t="n">
-        <v>6338968</v>
+        <v>6338963</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6165,6 +6165,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,10 +6196,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123973504</v>
+        <v>123972575</v>
       </c>
       <c r="B52" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6203,46 +6208,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575611</v>
+        <v>575396</v>
       </c>
       <c r="R52" t="n">
-        <v>6338932</v>
+        <v>6338959</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -5778,10 +5778,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123972575</v>
+        <v>123972955</v>
       </c>
       <c r="B48" t="n">
-        <v>95705</v>
+        <v>100279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5794,21 +5794,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5818,10 +5818,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575396</v>
+        <v>575485</v>
       </c>
       <c r="R48" t="n">
-        <v>6338959</v>
+        <v>6338876</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123972955</v>
+        <v>123972648</v>
       </c>
       <c r="B49" t="n">
-        <v>100279</v>
+        <v>90972</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5892,25 +5892,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>5445</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5920,10 +5920,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575485</v>
+        <v>575416</v>
       </c>
       <c r="R49" t="n">
-        <v>6338876</v>
+        <v>6338968</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123972648</v>
+        <v>123972575</v>
       </c>
       <c r="B50" t="n">
-        <v>90972</v>
+        <v>95705</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5994,25 +5994,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5445</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575416</v>
+        <v>575396</v>
       </c>
       <c r="R50" t="n">
-        <v>6338968</v>
+        <v>6338959</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6084,10 +6084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123973504</v>
+        <v>123972269</v>
       </c>
       <c r="B51" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6096,46 +6096,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575611</v>
+        <v>575366</v>
       </c>
       <c r="R51" t="n">
-        <v>6338932</v>
+        <v>6338963</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6165,6 +6160,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,10 +6191,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123972269</v>
+        <v>123973504</v>
       </c>
       <c r="B52" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6203,41 +6203,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575366</v>
+        <v>575611</v>
       </c>
       <c r="R52" t="n">
-        <v>6338963</v>
+        <v>6338932</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6267,11 +6272,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -5880,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123972648</v>
+        <v>123972575</v>
       </c>
       <c r="B49" t="n">
-        <v>90972</v>
+        <v>95705</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5892,25 +5892,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5445</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5920,10 +5920,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575416</v>
+        <v>575396</v>
       </c>
       <c r="R49" t="n">
-        <v>6338968</v>
+        <v>6338959</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5982,7 +5982,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123972575</v>
+        <v>123972269</v>
       </c>
       <c r="B50" t="n">
         <v>95705</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575396</v>
+        <v>575366</v>
       </c>
       <c r="R50" t="n">
-        <v>6338959</v>
+        <v>6338963</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6058,6 +6058,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6084,10 +6089,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123972269</v>
+        <v>123973504</v>
       </c>
       <c r="B51" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6096,41 +6101,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575366</v>
+        <v>575611</v>
       </c>
       <c r="R51" t="n">
-        <v>6338963</v>
+        <v>6338932</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6160,11 +6170,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,10 +6196,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123973504</v>
+        <v>123972648</v>
       </c>
       <c r="B52" t="n">
-        <v>57529</v>
+        <v>90972</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6207,42 +6212,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575611</v>
+        <v>575416</v>
       </c>
       <c r="R52" t="n">
-        <v>6338932</v>
+        <v>6338968</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -5676,10 +5676,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123973813</v>
+        <v>123972575</v>
       </c>
       <c r="B47" t="n">
-        <v>91413</v>
+        <v>95705</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5692,34 +5692,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4217</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575666</v>
+        <v>575396</v>
       </c>
       <c r="R47" t="n">
-        <v>6338964</v>
+        <v>6338959</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5778,10 +5778,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123972955</v>
+        <v>123973504</v>
       </c>
       <c r="B48" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5790,41 +5790,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575485</v>
+        <v>575611</v>
       </c>
       <c r="R48" t="n">
-        <v>6338876</v>
+        <v>6338932</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5880,10 +5885,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123972575</v>
+        <v>123972955</v>
       </c>
       <c r="B49" t="n">
-        <v>95705</v>
+        <v>100279</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5896,21 +5901,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5920,10 +5925,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575396</v>
+        <v>575485</v>
       </c>
       <c r="R49" t="n">
-        <v>6338959</v>
+        <v>6338876</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6089,10 +6094,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123973504</v>
+        <v>123972648</v>
       </c>
       <c r="B51" t="n">
-        <v>57529</v>
+        <v>90972</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6105,42 +6110,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575611</v>
+        <v>575416</v>
       </c>
       <c r="R51" t="n">
-        <v>6338932</v>
+        <v>6338968</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123972648</v>
+        <v>123973813</v>
       </c>
       <c r="B52" t="n">
-        <v>90972</v>
+        <v>91413</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6208,38 +6208,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5445</v>
+        <v>4217</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575416</v>
+        <v>575666</v>
       </c>
       <c r="R52" t="n">
-        <v>6338968</v>
+        <v>6338964</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -5676,10 +5676,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123972575</v>
+        <v>123972648</v>
       </c>
       <c r="B47" t="n">
-        <v>95705</v>
+        <v>90972</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5688,25 +5688,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>5445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575396</v>
+        <v>575416</v>
       </c>
       <c r="R47" t="n">
-        <v>6338959</v>
+        <v>6338968</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5885,10 +5885,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123972955</v>
+        <v>123972269</v>
       </c>
       <c r="B49" t="n">
-        <v>100279</v>
+        <v>95705</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5901,21 +5901,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5925,10 +5925,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575485</v>
+        <v>575366</v>
       </c>
       <c r="R49" t="n">
-        <v>6338876</v>
+        <v>6338963</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5961,6 +5961,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5987,7 +5992,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123972269</v>
+        <v>123972575</v>
       </c>
       <c r="B50" t="n">
         <v>95705</v>
@@ -6027,10 +6032,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575366</v>
+        <v>575396</v>
       </c>
       <c r="R50" t="n">
-        <v>6338963</v>
+        <v>6338959</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6063,11 +6068,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6094,10 +6094,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123972648</v>
+        <v>123973813</v>
       </c>
       <c r="B51" t="n">
-        <v>90972</v>
+        <v>91413</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6106,38 +6106,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5445</v>
+        <v>4217</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575416</v>
+        <v>575666</v>
       </c>
       <c r="R51" t="n">
-        <v>6338968</v>
+        <v>6338964</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6196,10 +6196,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123973813</v>
+        <v>123972955</v>
       </c>
       <c r="B52" t="n">
-        <v>91413</v>
+        <v>100279</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6212,34 +6212,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4217</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575666</v>
+        <v>575485</v>
       </c>
       <c r="R52" t="n">
-        <v>6338964</v>
+        <v>6338876</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -5778,10 +5778,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123973504</v>
+        <v>123972269</v>
       </c>
       <c r="B48" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5790,46 +5790,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575611</v>
+        <v>575366</v>
       </c>
       <c r="R48" t="n">
-        <v>6338932</v>
+        <v>6338963</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5859,6 +5854,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5885,10 +5885,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123972269</v>
+        <v>123973504</v>
       </c>
       <c r="B49" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5897,41 +5897,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575366</v>
+        <v>575611</v>
       </c>
       <c r="R49" t="n">
-        <v>6338963</v>
+        <v>6338932</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5961,11 +5966,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 53162-2022 artfynd.xlsx
+++ b/artfynd/A 53162-2022 artfynd.xlsx
@@ -5778,10 +5778,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123972269</v>
+        <v>123973813</v>
       </c>
       <c r="B48" t="n">
-        <v>95705</v>
+        <v>91413</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5794,34 +5794,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>4217</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575366</v>
+        <v>575666</v>
       </c>
       <c r="R48" t="n">
-        <v>6338963</v>
+        <v>6338964</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5854,11 +5854,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5885,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123973504</v>
+        <v>123972575</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5897,46 +5892,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575611</v>
+        <v>575396</v>
       </c>
       <c r="R49" t="n">
-        <v>6338932</v>
+        <v>6338959</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5992,10 +5982,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123972575</v>
+        <v>123972955</v>
       </c>
       <c r="B50" t="n">
-        <v>95705</v>
+        <v>100279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6008,21 +5998,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6032,10 +6022,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575396</v>
+        <v>575485</v>
       </c>
       <c r="R50" t="n">
-        <v>6338959</v>
+        <v>6338876</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6094,10 +6084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123973813</v>
+        <v>123973504</v>
       </c>
       <c r="B51" t="n">
-        <v>91413</v>
+        <v>57529</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6106,41 +6096,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575666</v>
+        <v>575611</v>
       </c>
       <c r="R51" t="n">
-        <v>6338964</v>
+        <v>6338932</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6196,10 +6191,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123972955</v>
+        <v>123972269</v>
       </c>
       <c r="B52" t="n">
-        <v>100279</v>
+        <v>95705</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6212,21 +6207,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6236,10 +6231,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575485</v>
+        <v>575366</v>
       </c>
       <c r="R52" t="n">
-        <v>6338876</v>
+        <v>6338963</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6272,6 +6267,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Stor kudde (60 cm bred och 30 cm hög) som håller på att dö för att det avverkats för nära. Skogen avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD52" t="b">
